--- a/data/trans_orig/IP07C16-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP07C16-Habitat-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de haber podido estar al aire libre en 2007 (tasa de respuesta: 89,29%)</t>
+          <t>Menores según la frecuencia de haber podido estar al aire libre en 2007 (tasa de respuesta: 89,29%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>13443</t>
+          <t>14081</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>25206</t>
+          <t>25783</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>23,38%</t>
+          <t>24,49%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>43,84%</t>
+          <t>44,84%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>19761</t>
+          <t>19923</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>32185</t>
+          <t>32101</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>29,07%</t>
+          <t>29,31%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>47,35%</t>
+          <t>47,23%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>36668</t>
+          <t>36109</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>53289</t>
+          <t>54084</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>29,22%</t>
+          <t>28,78%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>42,47%</t>
+          <t>43,1%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>23091</t>
+          <t>22983</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>35419</t>
+          <t>35608</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>40,16%</t>
+          <t>39,97%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>61,6%</t>
+          <t>61,92%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>25916</t>
+          <t>26022</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>39111</t>
+          <t>39828</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>38,13%</t>
+          <t>38,28%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>57,54%</t>
+          <t>58,6%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>53535</t>
+          <t>52139</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>71755</t>
+          <t>71301</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>42,67%</t>
+          <t>41,55%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>57,19%</t>
+          <t>56,83%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4030</t>
+          <t>4182</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>12397</t>
+          <t>13023</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>21,56%</t>
+          <t>22,65%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>5173</t>
+          <t>5598</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>14390</t>
+          <t>14658</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>21,17%</t>
+          <t>21,57%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>11389</t>
+          <t>11460</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>24429</t>
+          <t>24189</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>19,47%</t>
+          <t>19,28%</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4262</t>
+          <t>4399</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1146,7 +1146,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>4478</t>
+          <t>4224</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,37%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>30640</t>
+          <t>30272</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>45728</t>
+          <t>45671</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>30,89%</t>
+          <t>30,52%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>46,11%</t>
+          <t>46,05%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>32498</t>
+          <t>32589</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>47772</t>
+          <t>47598</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>35,28%</t>
+          <t>35,38%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>51,87%</t>
+          <t>51,68%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>67728</t>
+          <t>67800</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>88584</t>
+          <t>89947</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>35,41%</t>
+          <t>35,44%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>46,31%</t>
+          <t>47,02%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>39222</t>
+          <t>38226</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>53562</t>
+          <t>54053</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>39,55%</t>
+          <t>38,54%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>54,0%</t>
+          <t>54,5%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>31605</t>
+          <t>31789</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>47057</t>
+          <t>46408</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>34,31%</t>
+          <t>34,51%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>51,09%</t>
+          <t>50,39%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>74371</t>
+          <t>73931</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>95944</t>
+          <t>95637</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>38,88%</t>
+          <t>38,65%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>50,16%</t>
+          <t>50,0%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>8349</t>
+          <t>8602</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>19387</t>
+          <t>19281</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>19,55%</t>
+          <t>19,44%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>5887</t>
+          <t>5672</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>15068</t>
+          <t>14779</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>16,36%</t>
+          <t>16,05%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>16288</t>
+          <t>15982</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>30568</t>
+          <t>29869</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>15,98%</t>
+          <t>15,61%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>661</t>
+          <t>662</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5422</t>
+          <t>6066</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,7 +1773,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>685</t>
+          <t>683</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6222</t>
+          <t>6856</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,7 +1808,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2051</t>
+          <t>2060</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>9463</t>
+          <t>10106</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>5,28%</t>
         </is>
       </c>
     </row>
@@ -1906,7 +1906,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3444</t>
+          <t>4278</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,7 +1941,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3854</t>
+          <t>4098</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,14%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>20579</t>
+          <t>20441</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>31667</t>
+          <t>31657</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>38,21%</t>
+          <t>37,95%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>58,79%</t>
+          <t>58,77%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>17187</t>
+          <t>17106</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>29141</t>
+          <t>29429</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>28,3%</t>
+          <t>28,16%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>47,98%</t>
+          <t>48,46%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>41112</t>
+          <t>40504</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>57466</t>
+          <t>57721</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>35,87%</t>
+          <t>35,34%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>50,14%</t>
+          <t>50,37%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>16863</t>
+          <t>16646</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>27753</t>
+          <t>27695</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>31,31%</t>
+          <t>30,9%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>51,52%</t>
+          <t>51,42%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>24707</t>
+          <t>24811</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>36428</t>
+          <t>36528</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>40,68%</t>
+          <t>40,85%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>59,98%</t>
+          <t>60,14%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>44393</t>
+          <t>43881</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>61828</t>
+          <t>62176</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>38,74%</t>
+          <t>38,29%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>53,95%</t>
+          <t>54,25%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2590</t>
+          <t>2804</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>9348</t>
+          <t>9177</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>17,35%</t>
+          <t>17,04%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2772</t>
+          <t>2806</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>10291</t>
+          <t>9893</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>16,94%</t>
+          <t>16,29%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>6715</t>
+          <t>6675</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>17000</t>
+          <t>16728</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>14,6%</t>
         </is>
       </c>
     </row>
@@ -2440,7 +2440,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2665</t>
+          <t>3105</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2455,7 +2455,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,7 +2475,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4108</t>
+          <t>4124</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2490,7 +2490,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>481</t>
+          <t>479</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>4875</t>
+          <t>4598</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2525,7 +2525,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,01%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>29003</t>
+          <t>29254</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>43537</t>
+          <t>45489</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>37,04%</t>
+          <t>37,36%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>55,6%</t>
+          <t>58,09%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>29020</t>
+          <t>29141</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>43773</t>
+          <t>43844</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>33,44%</t>
+          <t>33,58%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>50,45%</t>
+          <t>50,53%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>63091</t>
+          <t>63230</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>84585</t>
+          <t>83855</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>38,22%</t>
+          <t>38,3%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>51,24%</t>
+          <t>50,8%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>16546</t>
+          <t>16232</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>29509</t>
+          <t>29801</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>21,13%</t>
+          <t>20,73%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>37,68%</t>
+          <t>38,06%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>25774</t>
+          <t>26036</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>39910</t>
+          <t>40746</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>29,7%</t>
+          <t>30,01%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>46,0%</t>
+          <t>46,96%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>45946</t>
+          <t>46288</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>65840</t>
+          <t>65774</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>27,83%</t>
+          <t>28,04%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>39,88%</t>
+          <t>39,84%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>8416</t>
+          <t>7672</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>20554</t>
+          <t>19246</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>26,25%</t>
+          <t>24,58%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>10551</t>
+          <t>10576</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>21742</t>
+          <t>22343</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>12,19%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>25,06%</t>
+          <t>25,75%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>21535</t>
+          <t>21291</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>36769</t>
+          <t>37447</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>13,05%</t>
+          <t>12,9%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>22,27%</t>
+          <t>22,68%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1450</t>
+          <t>1504</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>8297</t>
+          <t>8566</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>10,6%</t>
+          <t>10,94%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>567</t>
+          <t>568</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>4642</t>
+          <t>4736</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3172,7 +3172,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2708</t>
+          <t>2724</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>10904</t>
+          <t>10547</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,39%</t>
         </is>
       </c>
     </row>
@@ -3235,7 +3235,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>4953</t>
+          <t>5334</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3250,7 +3250,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3305,7 +3305,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5209</t>
+          <t>5346</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3320,7 +3320,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,24%</t>
         </is>
       </c>
     </row>
@@ -3460,12 +3460,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>107476</t>
+          <t>106768</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>133334</t>
+          <t>134817</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3475,12 +3475,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>37,21%</t>
+          <t>36,96%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>46,16%</t>
+          <t>46,67%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>112214</t>
+          <t>111628</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>138585</t>
+          <t>138578</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>36,48%</t>
+          <t>36,29%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>45,06%</t>
+          <t>45,05%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>227729</t>
+          <t>227110</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>263319</t>
+          <t>265743</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>38,18%</t>
+          <t>38,08%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>44,15%</t>
+          <t>44,56%</t>
         </is>
       </c>
     </row>
@@ -3573,12 +3573,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>107019</t>
+          <t>107171</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>132199</t>
+          <t>134159</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3588,12 +3588,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>37,05%</t>
+          <t>37,1%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>45,77%</t>
+          <t>46,44%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>122374</t>
+          <t>122234</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>149263</t>
+          <t>148911</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>39,79%</t>
+          <t>39,74%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>48,53%</t>
+          <t>48,41%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3643,12 +3643,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>238069</t>
+          <t>236164</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>272780</t>
+          <t>277010</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>39,92%</t>
+          <t>39,6%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>45,74%</t>
+          <t>46,44%</t>
         </is>
       </c>
     </row>
@@ -3686,12 +3686,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>30199</t>
+          <t>30084</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>48446</t>
+          <t>48631</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3701,12 +3701,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>10,41%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>16,77%</t>
+          <t>16,84%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3721,12 +3721,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>32094</t>
+          <t>31900</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>50515</t>
+          <t>51044</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>10,37%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>16,42%</t>
+          <t>16,6%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3756,12 +3756,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>67207</t>
+          <t>66893</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>93084</t>
+          <t>94589</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>11,22%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>15,61%</t>
+          <t>15,86%</t>
         </is>
       </c>
     </row>
@@ -3799,12 +3799,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>3817</t>
+          <t>4104</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>13689</t>
+          <t>12905</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3814,12 +3814,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3834,12 +3834,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>2667</t>
+          <t>2742</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>10481</t>
+          <t>10504</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3869,12 +3869,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>8452</t>
+          <t>8693</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>21307</t>
+          <t>21547</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,61%</t>
         </is>
       </c>
     </row>
@@ -3917,7 +3917,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>5319</t>
+          <t>5307</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3952,7 +3952,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>3436</t>
+          <t>4194</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3967,7 +3967,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3982,12 +3982,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>684</t>
+          <t>683</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>6026</t>
+          <t>5936</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4002,7 +4002,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,0%</t>
         </is>
       </c>
     </row>
@@ -4179,7 +4179,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de haber podido estar al aire libre en 2012 (tasa de respuesta: 95,2%)</t>
+          <t>Menores según la frecuencia de haber podido estar al aire libre en 2012 (tasa de respuesta: 95,2%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4374,12 +4374,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>26697</t>
+          <t>27237</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>40459</t>
+          <t>41038</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4389,12 +4389,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>42,08%</t>
+          <t>42,93%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>63,77%</t>
+          <t>64,68%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4409,12 +4409,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>30201</t>
+          <t>30795</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>44852</t>
+          <t>44658</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4424,12 +4424,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>41,96%</t>
+          <t>42,79%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>62,31%</t>
+          <t>62,04%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4444,12 +4444,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>62782</t>
+          <t>61536</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>81260</t>
+          <t>81877</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4459,12 +4459,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>46,36%</t>
+          <t>45,44%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>60,01%</t>
+          <t>60,46%</t>
         </is>
       </c>
     </row>
@@ -4487,12 +4487,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>14804</t>
+          <t>15401</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>27735</t>
+          <t>27594</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4502,12 +4502,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>23,33%</t>
+          <t>24,27%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>43,71%</t>
+          <t>43,49%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4522,12 +4522,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>19167</t>
+          <t>18692</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>32953</t>
+          <t>32024</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4537,12 +4537,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>26,63%</t>
+          <t>25,97%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>45,78%</t>
+          <t>44,49%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4557,12 +4557,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>38110</t>
+          <t>37251</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>56502</t>
+          <t>56703</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4572,12 +4572,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>28,14%</t>
+          <t>27,51%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>41,72%</t>
+          <t>41,87%</t>
         </is>
       </c>
     </row>
@@ -4600,12 +4600,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4066</t>
+          <t>4222</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>12988</t>
+          <t>13362</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4615,12 +4615,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>20,47%</t>
+          <t>21,06%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4635,12 +4635,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>4121</t>
+          <t>4553</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>13103</t>
+          <t>13282</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>18,45%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4670,12 +4670,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>9951</t>
+          <t>9868</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>22378</t>
+          <t>22936</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>16,94%</t>
         </is>
       </c>
     </row>
@@ -4753,7 +4753,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2766</t>
+          <t>3527</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>4118</t>
+          <t>3773</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4803,7 +4803,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>2,79%</t>
         </is>
       </c>
     </row>
@@ -4831,7 +4831,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4580</t>
+          <t>4602</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4846,7 +4846,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4901,7 +4901,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3690</t>
+          <t>5522</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4916,7 +4916,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>4,08%</t>
         </is>
       </c>
     </row>
@@ -5056,12 +5056,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>40846</t>
+          <t>40050</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>56967</t>
+          <t>56741</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5071,12 +5071,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>42,3%</t>
+          <t>41,48%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>59,0%</t>
+          <t>58,77%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5091,12 +5091,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>37877</t>
+          <t>38689</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>53499</t>
+          <t>53539</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5106,12 +5106,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>40,06%</t>
+          <t>40,92%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>56,58%</t>
+          <t>56,62%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5126,12 +5126,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>83944</t>
+          <t>83485</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>105590</t>
+          <t>105848</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>43,93%</t>
+          <t>43,69%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>55,25%</t>
+          <t>55,39%</t>
         </is>
       </c>
     </row>
@@ -5169,12 +5169,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>30978</t>
+          <t>30403</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>46547</t>
+          <t>45913</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5184,12 +5184,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>32,08%</t>
+          <t>31,49%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>48,21%</t>
+          <t>47,55%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5204,12 +5204,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>32600</t>
+          <t>34081</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>48223</t>
+          <t>48779</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>34,48%</t>
+          <t>36,04%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>51,0%</t>
+          <t>51,59%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5239,12 +5239,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>67983</t>
+          <t>68335</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>89241</t>
+          <t>90068</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>35,57%</t>
+          <t>35,76%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>46,7%</t>
+          <t>47,13%</t>
         </is>
       </c>
     </row>
@@ -5282,12 +5282,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4518</t>
+          <t>5077</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>13918</t>
+          <t>14150</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>14,41%</t>
+          <t>14,66%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5317,12 +5317,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>3806</t>
+          <t>3935</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>12297</t>
+          <t>12465</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>13,18%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>10793</t>
+          <t>10409</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>23345</t>
+          <t>22757</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>11,91%</t>
         </is>
       </c>
     </row>
@@ -5400,7 +5400,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3994</t>
+          <t>4662</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5415,7 +5415,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5470,7 +5470,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4015</t>
+          <t>4621</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5485,7 +5485,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,42%</t>
         </is>
       </c>
     </row>
@@ -5548,7 +5548,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3289</t>
+          <t>3273</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5563,7 +5563,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5583,7 +5583,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3156</t>
+          <t>3239</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5598,7 +5598,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,69%</t>
         </is>
       </c>
     </row>
@@ -5738,12 +5738,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>21830</t>
+          <t>21721</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>34441</t>
+          <t>34552</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5753,12 +5753,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>33,5%</t>
+          <t>33,33%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>52,85%</t>
+          <t>53,02%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5773,12 +5773,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>31975</t>
+          <t>32020</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>44278</t>
+          <t>44456</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>46,91%</t>
+          <t>46,98%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>64,96%</t>
+          <t>65,23%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5808,12 +5808,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>57117</t>
+          <t>57873</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>74986</t>
+          <t>75196</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>42,84%</t>
+          <t>43,41%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>56,24%</t>
+          <t>56,4%</t>
         </is>
       </c>
     </row>
@@ -5851,12 +5851,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>21597</t>
+          <t>21738</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>34510</t>
+          <t>34042</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5866,12 +5866,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>33,14%</t>
+          <t>33,36%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>52,96%</t>
+          <t>52,24%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5886,12 +5886,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>12509</t>
+          <t>11872</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>23221</t>
+          <t>23666</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5901,12 +5901,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18,35%</t>
+          <t>17,42%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>34,07%</t>
+          <t>34,72%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5921,12 +5921,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>36523</t>
+          <t>36509</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>53692</t>
+          <t>54041</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5936,12 +5936,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>27,39%</t>
+          <t>27,38%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>40,27%</t>
+          <t>40,53%</t>
         </is>
       </c>
     </row>
@@ -5964,12 +5964,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>4529</t>
+          <t>4873</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>12699</t>
+          <t>13146</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5979,12 +5979,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>19,49%</t>
+          <t>20,17%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>5953</t>
+          <t>5967</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>14703</t>
+          <t>15238</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>21,57%</t>
+          <t>22,36%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>12906</t>
+          <t>12517</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>24882</t>
+          <t>25432</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>18,66%</t>
+          <t>19,08%</t>
         </is>
       </c>
     </row>
@@ -6082,7 +6082,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4321</t>
+          <t>4578</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6097,7 +6097,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6117,7 +6117,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3098</t>
+          <t>3145</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6132,7 +6132,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>593</t>
+          <t>597</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>5066</t>
+          <t>5577</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>4,18%</t>
         </is>
       </c>
     </row>
@@ -6225,12 +6225,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>566</t>
+          <t>578</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>4339</t>
+          <t>4920</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6240,12 +6240,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>580</t>
+          <t>577</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>5373</t>
+          <t>4789</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6280,7 +6280,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>3,59%</t>
         </is>
       </c>
     </row>
@@ -6420,12 +6420,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>26471</t>
+          <t>27181</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>41827</t>
+          <t>43445</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6435,12 +6435,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>30,88%</t>
+          <t>31,71%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>48,79%</t>
+          <t>50,68%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6455,12 +6455,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>28545</t>
+          <t>27596</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>44251</t>
+          <t>43059</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6470,12 +6470,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>32,03%</t>
+          <t>30,97%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>49,66%</t>
+          <t>48,32%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6490,12 +6490,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>59292</t>
+          <t>58508</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>81017</t>
+          <t>80159</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6505,12 +6505,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>33,91%</t>
+          <t>33,46%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>46,34%</t>
+          <t>45,85%</t>
         </is>
       </c>
     </row>
@@ -6533,12 +6533,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>28627</t>
+          <t>28772</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>44180</t>
+          <t>45562</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6548,12 +6548,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>33,39%</t>
+          <t>33,56%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>51,54%</t>
+          <t>53,15%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6568,12 +6568,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>27422</t>
+          <t>27523</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>42944</t>
+          <t>43608</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>30,77%</t>
+          <t>30,89%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>48,19%</t>
+          <t>48,94%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6603,12 +6603,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>60854</t>
+          <t>61451</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>82805</t>
+          <t>83654</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6618,12 +6618,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>34,81%</t>
+          <t>35,15%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>47,36%</t>
+          <t>47,85%</t>
         </is>
       </c>
     </row>
@@ -6646,12 +6646,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>7372</t>
+          <t>7162</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>18856</t>
+          <t>18707</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6661,12 +6661,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>22,0%</t>
+          <t>21,82%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6681,12 +6681,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>12084</t>
+          <t>11794</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>24935</t>
+          <t>24584</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6696,12 +6696,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>13,56%</t>
+          <t>13,24%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>27,98%</t>
+          <t>27,59%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6716,12 +6716,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>21684</t>
+          <t>21962</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>38500</t>
+          <t>38294</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6731,12 +6731,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>12,56%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>22,02%</t>
+          <t>21,9%</t>
         </is>
       </c>
     </row>
@@ -6759,54 +6759,54 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
+          <t>594</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>6283</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>2,63%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>0,69%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>7,33%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>6138</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>2,63%</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>7,16%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
           <t>—%</t>
@@ -6829,12 +6829,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>592</t>
+          <t>595</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>6394</t>
+          <t>6383</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6849,7 +6849,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,65%</t>
         </is>
       </c>
     </row>
@@ -6912,7 +6912,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>4179</t>
+          <t>4215</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6927,7 +6927,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6947,7 +6947,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>4121</t>
+          <t>4080</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6962,7 +6962,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,33%</t>
         </is>
       </c>
     </row>
@@ -7102,12 +7102,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>131633</t>
+          <t>130908</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>161209</t>
+          <t>160430</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>42,34%</t>
+          <t>42,11%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>51,85%</t>
+          <t>51,6%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7137,12 +7137,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>145107</t>
+          <t>140888</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>173775</t>
+          <t>171065</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7152,12 +7152,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>44,81%</t>
+          <t>43,51%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>53,67%</t>
+          <t>52,83%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7172,12 +7172,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>282303</t>
+          <t>284324</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>322660</t>
+          <t>324255</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7187,12 +7187,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>44,48%</t>
+          <t>44,8%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>50,84%</t>
+          <t>51,09%</t>
         </is>
       </c>
     </row>
@@ -7215,12 +7215,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>109959</t>
+          <t>109008</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>137522</t>
+          <t>137725</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>35,37%</t>
+          <t>35,06%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>44,24%</t>
+          <t>44,3%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7250,12 +7250,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>105097</t>
+          <t>104619</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>134851</t>
+          <t>134653</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7265,12 +7265,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>32,46%</t>
+          <t>32,31%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>41,65%</t>
+          <t>41,59%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7285,12 +7285,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>223408</t>
+          <t>222853</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>262436</t>
+          <t>263010</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7300,12 +7300,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>35,2%</t>
+          <t>35,11%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>41,35%</t>
+          <t>41,44%</t>
         </is>
       </c>
     </row>
@@ -7328,12 +7328,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>28262</t>
+          <t>28458</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>46525</t>
+          <t>47279</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7343,12 +7343,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>14,97%</t>
+          <t>15,21%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7363,12 +7363,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>32871</t>
+          <t>33550</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>52274</t>
+          <t>52875</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7378,12 +7378,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>16,14%</t>
+          <t>16,33%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7398,12 +7398,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>66040</t>
+          <t>65083</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>93579</t>
+          <t>92040</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7413,12 +7413,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>10,25%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>14,74%</t>
+          <t>14,5%</t>
         </is>
       </c>
     </row>
@@ -7441,12 +7441,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2156</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>9456</t>
+          <t>9753</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7456,12 +7456,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -7481,7 +7481,7 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>4549</t>
+          <t>4493</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7496,7 +7496,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -7511,12 +7511,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>3221</t>
+          <t>3203</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>11626</t>
+          <t>11284</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -7526,12 +7526,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,78%</t>
         </is>
       </c>
     </row>
@@ -7559,7 +7559,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>4560</t>
+          <t>4590</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7574,7 +7574,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7589,12 +7589,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>1258</t>
+          <t>1192</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>7507</t>
+          <t>7109</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7604,12 +7604,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7624,12 +7624,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1523</t>
+          <t>1820</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>8477</t>
+          <t>9564</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7639,12 +7639,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,51%</t>
         </is>
       </c>
     </row>
@@ -7821,7 +7821,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de haber podido estar al aire libre en 2016 (tasa de respuesta: 95,47%)</t>
+          <t>Menores según la frecuencia de haber podido estar al aire libre en 2016 (tasa de respuesta: 95,47%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8016,12 +8016,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>25564</t>
+          <t>26487</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>40154</t>
+          <t>40321</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>37,05%</t>
+          <t>38,38%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>58,19%</t>
+          <t>58,43%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8051,12 +8051,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>22571</t>
+          <t>22748</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>36239</t>
+          <t>36736</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8066,12 +8066,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>32,25%</t>
+          <t>32,5%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>51,77%</t>
+          <t>52,48%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8086,12 +8086,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>51694</t>
+          <t>52255</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>72432</t>
+          <t>71382</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8101,12 +8101,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>37,19%</t>
+          <t>37,59%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>52,11%</t>
+          <t>51,35%</t>
         </is>
       </c>
     </row>
@@ -8129,12 +8129,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>20000</t>
+          <t>20174</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>34393</t>
+          <t>34426</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>28,98%</t>
+          <t>29,24%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>49,84%</t>
+          <t>49,89%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8164,12 +8164,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>23992</t>
+          <t>23751</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>38346</t>
+          <t>38125</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8179,12 +8179,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>34,28%</t>
+          <t>33,93%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>54,78%</t>
+          <t>54,47%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8199,12 +8199,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>47994</t>
+          <t>48800</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>68480</t>
+          <t>69436</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8214,12 +8214,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>34,53%</t>
+          <t>35,11%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>49,27%</t>
+          <t>49,95%</t>
         </is>
       </c>
     </row>
@@ -8242,12 +8242,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4891</t>
+          <t>4828</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>14546</t>
+          <t>14394</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8257,12 +8257,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>21,08%</t>
+          <t>20,86%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8277,12 +8277,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>5518</t>
+          <t>5598</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>15978</t>
+          <t>16552</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8292,12 +8292,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>22,83%</t>
+          <t>23,65%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8312,12 +8312,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>13055</t>
+          <t>12403</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>26922</t>
+          <t>26014</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8327,12 +8327,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>19,37%</t>
+          <t>18,71%</t>
         </is>
       </c>
     </row>
@@ -8698,12 +8698,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>34050</t>
+          <t>33544</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>49944</t>
+          <t>49266</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8713,12 +8713,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>33,09%</t>
+          <t>32,6%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>48,54%</t>
+          <t>47,88%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8733,12 +8733,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>39786</t>
+          <t>38863</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>57030</t>
+          <t>55601</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8748,12 +8748,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>38,48%</t>
+          <t>37,59%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>55,16%</t>
+          <t>53,78%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8768,12 +8768,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>77875</t>
+          <t>77309</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>100369</t>
+          <t>101723</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8783,12 +8783,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>37,75%</t>
+          <t>37,48%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>48,65%</t>
+          <t>49,31%</t>
         </is>
       </c>
     </row>
@@ -8811,12 +8811,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>37607</t>
+          <t>37502</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>54205</t>
+          <t>53700</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8826,12 +8826,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>36,55%</t>
+          <t>36,45%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>52,68%</t>
+          <t>52,19%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8846,12 +8846,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>31636</t>
+          <t>31304</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>48093</t>
+          <t>47628</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8861,12 +8861,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>30,6%</t>
+          <t>30,28%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>46,51%</t>
+          <t>46,06%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8881,12 +8881,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>73276</t>
+          <t>71537</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>95554</t>
+          <t>95044</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8896,12 +8896,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>35,52%</t>
+          <t>34,68%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>46,32%</t>
+          <t>46,07%</t>
         </is>
       </c>
     </row>
@@ -8924,12 +8924,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>7407</t>
+          <t>7495</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>17794</t>
+          <t>18109</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8939,12 +8939,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>17,29%</t>
+          <t>17,6%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8959,12 +8959,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>8944</t>
+          <t>8373</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>20618</t>
+          <t>20557</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8974,12 +8974,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>19,94%</t>
+          <t>19,88%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8994,12 +8994,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>18676</t>
+          <t>18895</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>34724</t>
+          <t>34580</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9009,12 +9009,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>16,76%</t>
         </is>
       </c>
     </row>
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>786</t>
+          <t>859</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7423</t>
+          <t>7249</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9052,12 +9052,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9072,12 +9072,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>691</t>
+          <t>676</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6742</t>
+          <t>6813</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9087,12 +9087,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2571</t>
+          <t>2428</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>10995</t>
+          <t>11014</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9122,12 +9122,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,34%</t>
         </is>
       </c>
     </row>
@@ -9155,7 +9155,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3782</t>
+          <t>4340</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9170,7 +9170,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9225,7 +9225,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3771</t>
+          <t>3744</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9240,7 +9240,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,81%</t>
         </is>
       </c>
     </row>
@@ -9380,12 +9380,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>28689</t>
+          <t>29150</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>42702</t>
+          <t>42437</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9395,12 +9395,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>41,04%</t>
+          <t>41,7%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>61,08%</t>
+          <t>60,7%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>27152</t>
+          <t>27903</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>41799</t>
+          <t>42238</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9430,12 +9430,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>36,39%</t>
+          <t>37,39%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>56,01%</t>
+          <t>56,6%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9450,12 +9450,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>61154</t>
+          <t>60187</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>80752</t>
+          <t>80337</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9465,12 +9465,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>42,31%</t>
+          <t>41,64%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>55,87%</t>
+          <t>55,59%</t>
         </is>
       </c>
     </row>
@@ -9493,12 +9493,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>17150</t>
+          <t>17202</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>30107</t>
+          <t>30047</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9508,12 +9508,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>24,53%</t>
+          <t>24,61%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>43,07%</t>
+          <t>42,98%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9528,12 +9528,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>22901</t>
+          <t>22322</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>38304</t>
+          <t>36976</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9543,12 +9543,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>30,69%</t>
+          <t>29,91%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>51,33%</t>
+          <t>49,55%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9563,12 +9563,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>43168</t>
+          <t>43661</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>62290</t>
+          <t>62914</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9578,12 +9578,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>29,87%</t>
+          <t>30,21%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>43,1%</t>
+          <t>43,53%</t>
         </is>
       </c>
     </row>
@@ -9606,12 +9606,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>6360</t>
+          <t>5935</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>15790</t>
+          <t>16148</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9621,47 +9621,47 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
+          <t>8,49%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>23,1%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>6792</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>3351</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>12326</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
           <t>9,1%</t>
         </is>
       </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>22,59%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>6792</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>3439</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>11925</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>9,1%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>15,98%</t>
+          <t>16,52%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9676,12 +9676,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>11209</t>
+          <t>11219</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>24272</t>
+          <t>24603</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9696,7 +9696,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>16,79%</t>
+          <t>17,02%</t>
         </is>
       </c>
     </row>
@@ -9724,7 +9724,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3171</t>
+          <t>2944</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9739,7 +9739,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9754,12 +9754,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>753</t>
+          <t>724</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>7697</t>
+          <t>7044</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9769,12 +9769,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>9,44%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9789,12 +9789,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1326</t>
+          <t>1272</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>8305</t>
+          <t>8030</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9804,12 +9804,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,56%</t>
         </is>
       </c>
     </row>
@@ -10062,12 +10062,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>27029</t>
+          <t>28157</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>44613</t>
+          <t>44494</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10077,12 +10077,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>26,2%</t>
+          <t>27,29%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>43,25%</t>
+          <t>43,13%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10097,12 +10097,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>30032</t>
+          <t>30682</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>46677</t>
+          <t>47311</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10112,12 +10112,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>30,17%</t>
+          <t>30,83%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>46,9%</t>
+          <t>47,54%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10132,12 +10132,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>64226</t>
+          <t>62564</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>86920</t>
+          <t>86138</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10147,12 +10147,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>31,69%</t>
+          <t>30,87%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>42,88%</t>
+          <t>42,5%</t>
         </is>
       </c>
     </row>
@@ -10175,12 +10175,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>33012</t>
+          <t>34044</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>50175</t>
+          <t>50225</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10190,12 +10190,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>32,0%</t>
+          <t>33,0%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>48,64%</t>
+          <t>48,69%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10210,12 +10210,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>33041</t>
+          <t>33174</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>49478</t>
+          <t>49742</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10225,12 +10225,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>33,2%</t>
+          <t>33,33%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>49,71%</t>
+          <t>49,98%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10245,12 +10245,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>71554</t>
+          <t>71023</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>95010</t>
+          <t>94848</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10260,12 +10260,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>35,3%</t>
+          <t>35,04%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>46,87%</t>
+          <t>46,79%</t>
         </is>
       </c>
     </row>
@@ -10288,12 +10288,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>13656</t>
+          <t>13534</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>28146</t>
+          <t>27756</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10303,12 +10303,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>13,12%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>27,28%</t>
+          <t>26,91%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10323,12 +10323,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>11581</t>
+          <t>11717</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>23855</t>
+          <t>24433</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10338,12 +10338,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>11,77%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>23,97%</t>
+          <t>24,55%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10358,12 +10358,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>28366</t>
+          <t>28257</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>47266</t>
+          <t>46491</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -10373,12 +10373,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>13,94%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>23,32%</t>
+          <t>22,94%</t>
         </is>
       </c>
     </row>
@@ -10401,12 +10401,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1420</t>
+          <t>1397</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>7768</t>
+          <t>8138</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10436,12 +10436,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>710</t>
+          <t>706</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>6380</t>
+          <t>6630</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10456,7 +10456,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10471,12 +10471,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2973</t>
+          <t>2918</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>11398</t>
+          <t>12106</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10486,12 +10486,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,97%</t>
         </is>
       </c>
     </row>
@@ -10519,7 +10519,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>5718</t>
+          <t>5804</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10534,7 +10534,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10589,7 +10589,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5615</t>
+          <t>4915</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10604,7 +10604,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,42%</t>
         </is>
       </c>
     </row>
@@ -10744,12 +10744,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>130054</t>
+          <t>132149</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>162465</t>
+          <t>162357</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10759,12 +10759,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>37,7%</t>
+          <t>38,31%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>47,1%</t>
+          <t>47,06%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10779,12 +10779,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>135332</t>
+          <t>134576</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>166544</t>
+          <t>165548</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10794,12 +10794,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>38,94%</t>
+          <t>38,72%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>47,92%</t>
+          <t>47,63%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10814,12 +10814,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>275300</t>
+          <t>274918</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>318772</t>
+          <t>318754</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10829,7 +10829,7 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>39,75%</t>
+          <t>39,7%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -10857,12 +10857,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>121193</t>
+          <t>122242</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>152834</t>
+          <t>152691</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10872,12 +10872,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>35,13%</t>
+          <t>35,44%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>44,3%</t>
+          <t>44,26%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10892,12 +10892,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>124687</t>
+          <t>126125</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>155226</t>
+          <t>156471</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10907,12 +10907,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>35,88%</t>
+          <t>36,29%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>44,66%</t>
+          <t>45,02%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10927,12 +10927,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>256512</t>
+          <t>252808</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>300944</t>
+          <t>298504</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10942,12 +10942,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>37,04%</t>
+          <t>36,51%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>43,46%</t>
+          <t>43,1%</t>
         </is>
       </c>
     </row>
@@ -10970,12 +10970,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>40773</t>
+          <t>41040</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>62383</t>
+          <t>62274</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10985,12 +10985,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>11,9%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>18,05%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -11005,12 +11005,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>38480</t>
+          <t>37151</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>60807</t>
+          <t>58875</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -11020,12 +11020,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>10,69%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>17,5%</t>
+          <t>16,94%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11040,12 +11040,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>84450</t>
+          <t>84793</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>114198</t>
+          <t>116119</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -11055,12 +11055,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>12,24%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>16,77%</t>
         </is>
       </c>
     </row>
@@ -11083,12 +11083,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>3506</t>
+          <t>3678</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>12760</t>
+          <t>13233</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -11098,12 +11098,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -11118,12 +11118,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>4423</t>
+          <t>4389</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>14087</t>
+          <t>14831</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -11133,12 +11133,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -11153,12 +11153,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>9683</t>
+          <t>10009</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>23195</t>
+          <t>22903</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -11168,12 +11168,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,31%</t>
         </is>
       </c>
     </row>
@@ -11196,12 +11196,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>632</t>
+          <t>786</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>6674</t>
+          <t>6722</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -11211,12 +11211,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -11266,12 +11266,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>786</t>
+          <t>795</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>7122</t>
+          <t>7270</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -11286,7 +11286,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,05%</t>
         </is>
       </c>
     </row>
